--- a/fixtures/jeju/timetables/bis/raw/406006.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/406006.xlsx
@@ -6,8 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="532 화순-안덕-중문-대천-중앙R-오일장-하례리" r:id="rId3" sheetId="1"/>
-    <sheet name="532 하례리-오일장-중앙R-대천-중문-안덕-화순" r:id="rId4" sheetId="2"/>
+    <sheet name="532 하례리-오일장-중앙R-대천-중문-안덕-화순" r:id="rId3" sheetId="1"/>
+    <sheet name="532 화순-안덕-중문-대천-중앙R-오일장-하례리" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -18,10 +18,298 @@
     <t>구분</t>
   </si>
   <si>
+    <t>하례리입구</t>
+  </si>
+  <si>
+    <t>남주고</t>
+  </si>
+  <si>
+    <t>중앙R</t>
+  </si>
+  <si>
+    <t>법환농협</t>
+  </si>
+  <si>
+    <t>중문
+우체국</t>
+  </si>
+  <si>
+    <t>색 달</t>
+  </si>
+  <si>
+    <t>안덕계곡</t>
+  </si>
+  <si>
     <t>화순</t>
   </si>
   <si>
-    <t>안덕계곡</t>
+    <t>비  고</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>07:08</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>08:41</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>남주고 경유
+(평일)</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>11:51</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>14:34</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>16:01</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>17:09</t>
+  </si>
+  <si>
+    <t>17:16</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>18:21</t>
+  </si>
+  <si>
+    <t>18:36</t>
+  </si>
+  <si>
+    <t>18:59</t>
+  </si>
+  <si>
+    <t>19:06</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:37</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:22</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>20:41</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>20:57</t>
+  </si>
+  <si>
+    <t>21:11</t>
+  </si>
+  <si>
+    <t>21:26</t>
+  </si>
+  <si>
+    <t>21:49</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>22:08</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>532번</t>
+  </si>
+  <si>
+    <t>하례리입구-서귀포산업과학고등학교-법호촌입구-서귀포향토오일시장-중앙로터리(서) -청소년문화의집-삼매봉입구-서귀포여자고등학교-수모루-법환-강정-하원초등학교-중문고등학교-중문동주민센터-중문우체국-천제연폭포 -관광단지입구-색달-창천초등학교-안덕계곡-안덕농협-화순리</t>
+  </si>
+  <si>
+    <t>하례리입구→중앙R→
+법환농협→ 화순리</t>
+  </si>
+  <si>
+    <t>첫차(중앙R 줄발) 6:30, 막차 20:45, 배차간격 76~90분, 서귀포운수(064-732-4934)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2026. 3. 3.)</t>
   </si>
   <si>
     <t>색달</t>
@@ -30,22 +318,7 @@
     <t>중문우체국</t>
   </si>
   <si>
-    <t>법환농협</t>
-  </si>
-  <si>
-    <t>중앙R</t>
-  </si>
-  <si>
-    <t>남주고</t>
-  </si>
-  <si>
     <t>하례리 입구</t>
-  </si>
-  <si>
-    <t>비  고</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>06:27</t>
@@ -82,9 +355,6 @@
     <t>08:03</t>
   </si>
   <si>
-    <t>08:11</t>
-  </si>
-  <si>
     <t>08:33</t>
   </si>
   <si>
@@ -94,9 +364,6 @@
     <t>09:12</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>09:10</t>
   </si>
   <si>
@@ -106,9 +373,6 @@
     <t>09:29</t>
   </si>
   <si>
-    <t>09:37</t>
-  </si>
-  <si>
     <t>09:59</t>
   </si>
   <si>
@@ -130,9 +394,6 @@
     <t>11:03</t>
   </si>
   <si>
-    <t>11:25</t>
-  </si>
-  <si>
     <t>11:40</t>
   </si>
   <si>
@@ -151,9 +412,6 @@
     <t>12:28</t>
   </si>
   <si>
-    <t>12:50</t>
-  </si>
-  <si>
     <t>13:05</t>
   </si>
   <si>
@@ -170,9 +428,6 @@
   </si>
   <si>
     <t>13:53</t>
-  </si>
-  <si>
-    <t>14:15</t>
   </si>
   <si>
     <t>14:30</t>
@@ -287,9 +542,6 @@
 토평마을회관 종료</t>
   </si>
   <si>
-    <t>532번</t>
-  </si>
-  <si>
     <t>화순리-안덕농협-안덕계곡-창천초등학교-우남동-관광단지입구-천체연폭포-중문우체국-중문동주민센터-중문고등학교-하원초등학교-월평-강정-법환-수모루-서귀포여자고등학교-삼매봉-중앙로터리(동)-서귀포고등학교-서귀포향토오일시장-법호촌입구-서귀포산업과학고등학교-하례리입구</t>
   </si>
   <si>
@@ -298,258 +550,6 @@
   </si>
   <si>
     <t>첫차 6:27, 막차 20:51, 배차간격 76~90분, 서귀포운수(064-732-4934)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2026. 3. 3.)</t>
-  </si>
-  <si>
-    <t>하례리입구</t>
-  </si>
-  <si>
-    <t>중문
-우체국</t>
-  </si>
-  <si>
-    <t>색 달</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>07:08</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>07:34</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>07:42</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>08:41</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>남주고 경유
-(평일)</t>
-  </si>
-  <si>
-    <t>09:22</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>11:51</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>13:52</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>14:34</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:02</t>
-  </si>
-  <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>15:54</t>
-  </si>
-  <si>
-    <t>16:01</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>17:09</t>
-  </si>
-  <si>
-    <t>17:16</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:07</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
-    <t>18:36</t>
-  </si>
-  <si>
-    <t>18:59</t>
-  </si>
-  <si>
-    <t>19:06</t>
-  </si>
-  <si>
-    <t>19:18</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:37</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:22</t>
-  </si>
-  <si>
-    <t>20:34</t>
-  </si>
-  <si>
-    <t>20:41</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>20:57</t>
-  </si>
-  <si>
-    <t>21:11</t>
-  </si>
-  <si>
-    <t>21:26</t>
-  </si>
-  <si>
-    <t>21:49</t>
-  </si>
-  <si>
-    <t>21:56</t>
-  </si>
-  <si>
-    <t>22:08</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>하례리입구-서귀포산업과학고등학교-법호촌입구-서귀포향토오일시장-중앙로터리(서) -청소년문화의집-삼매봉입구-서귀포여자고등학교-수모루-법환-강정-하원초등학교-중문고등학교-중문동주민센터-중문우체국-천제연폭포 -관광단지입구-색달-창천초등학교-안덕계곡-안덕농협-화순리</t>
-  </si>
-  <si>
-    <t>하례리입구→중앙R→
-법환농협→ 화순리</t>
-  </si>
-  <si>
-    <t>첫차(중앙R 줄발) 6:30, 막차 20:45, 배차간격 76~90분, 서귀포운수(064-732-4934)</t>
   </si>
 </sst>
 </file>
@@ -942,13 +942,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -958,7 +958,7 @@
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -984,7 +984,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -994,7 +994,7 @@
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K5"/>
     </row>
@@ -1050,28 +1050,28 @@
         <v>10</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="I8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="J8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="K8" s="13" t="s">
         <v>17</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -1079,25 +1079,25 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="I9" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="J9" s="12" t="s">
         <v>25</v>
@@ -1111,31 +1111,31 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="I10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>33</v>
-      </c>
       <c r="K10" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -1143,31 +1143,31 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="I11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="J11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>40</v>
-      </c>
       <c r="K11" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -1175,31 +1175,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="H12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="I12" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="J12" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>47</v>
-      </c>
       <c r="K12" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -1207,31 +1207,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="F13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="H13" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="I13" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="J13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>54</v>
-      </c>
       <c r="K13" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -1239,25 +1239,25 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="I14" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>61</v>
@@ -1289,10 +1289,10 @@
         <v>67</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>26</v>
@@ -1303,28 +1303,28 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K16" s="13" t="s">
         <v>26</v>
@@ -1335,31 +1335,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -1367,28 +1367,28 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>26</v>
@@ -1425,7 +1425,7 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -1477,7 +1477,7 @@
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" s="23" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K5"/>
     </row>
@@ -1498,28 +1498,28 @@
         <v>0</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>2</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>9</v>
@@ -1533,28 +1533,28 @@
         <v>10</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -1562,31 +1562,31 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -1594,31 +1594,31 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D10" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>115</v>
-      </c>
       <c r="J10" s="28" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -1626,31 +1626,31 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D11" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>121</v>
-      </c>
       <c r="J11" s="28" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -1658,31 +1658,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D12" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>127</v>
-      </c>
       <c r="J12" s="28" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -1690,31 +1690,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D13" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>133</v>
-      </c>
       <c r="J13" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K13" s="29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -1722,31 +1722,31 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -1754,31 +1754,31 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K15" s="29" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -1786,31 +1786,31 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -1818,31 +1818,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D17" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>164</v>
-      </c>
       <c r="J17" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -1850,31 +1850,31 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H18" s="31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I18" s="31" t="s">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="J18" s="31" t="s">
         <v>173</v>
       </c>
       <c r="K18" s="32" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
